--- a/network/file/成绩登分册-2.xlsx
+++ b/network/file/成绩登分册-2.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\network\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B667A14F-5A8F-4DCC-8432-7C5305B69B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7DC626-8075-48B9-A697-3F83D4667B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A689E0DD-08C6-4720-86D0-7A22CF59F62D}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="8430" windowHeight="15585" xr2:uid="{A689E0DD-08C6-4720-86D0-7A22CF59F62D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="172">
   <si>
     <t>广州华立学院学生平时成绩登记表</t>
   </si>
@@ -521,11 +521,31 @@
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
-    <t>其它活动</t>
+    <t>全勤</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
-    <t>考试</t>
+    <t>期末考试</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>平时考试</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>表现</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>平时</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终成绩</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
@@ -533,7 +553,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -738,8 +758,22 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="8"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -934,19 +968,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1279,7 +1301,7 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1338,21 +1360,106 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="35" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1365,9 +1472,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1382,36 +1486,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1459,7 +1533,17 @@
     <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="注释" xfId="1" builtinId="10" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1533,13 +1617,13 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStylePreset3_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{9C61E0EB-A4F7-40EB-A631-0332C32841DE}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1814,130 +1898,159 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:V64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
     <col min="2" max="2" width="11.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="11.625" style="5" customWidth="1"/>
-    <col min="4" max="11" width="7.25" customWidth="1"/>
-    <col min="12" max="12" width="7.875" customWidth="1"/>
-    <col min="13" max="13" width="5" customWidth="1"/>
+    <col min="4" max="11" width="7.25" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="7.875" style="45" customWidth="1"/>
+    <col min="13" max="13" width="7.875" style="45" hidden="1" customWidth="1"/>
+    <col min="14" max="16" width="7.875" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="5" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="9" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="8.625" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:22" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-    </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="48" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+    </row>
+    <row r="2" spans="1:22" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49" t="s">
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49" t="s">
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="19"/>
-    </row>
-    <row r="3" spans="1:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="44" t="s">
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="19"/>
+    </row>
+    <row r="3" spans="1:22" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="37" t="s">
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="27" t="s">
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="R3" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="O3" s="2">
+      <c r="S3" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="32" t="s">
+    <row r="4" spans="1:22" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="54"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="50" t="s">
+      <c r="H4" s="53"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="54" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="K4" s="52" t="s">
         <v>165</v>
       </c>
-      <c r="J4" s="44" t="s">
+      <c r="L4" s="58"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+    </row>
+    <row r="5" spans="1:22" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="54"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="T5" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K4" s="32"/>
-      <c r="L4" s="37"/>
-    </row>
-    <row r="5" spans="1:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="44"/>
-      <c r="B5" s="45"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="37"/>
-    </row>
-    <row r="6" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V5" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
         <v>25</v>
       </c>
@@ -1948,16 +2061,34 @@
         <v>27</v>
       </c>
       <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
+      <c r="E6" s="10">
+        <v>60</v>
+      </c>
+      <c r="F6" s="10">
+        <v>60</v>
+      </c>
+      <c r="G6" s="10">
+        <v>60</v>
+      </c>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L6" s="30">
+        <v>66</v>
+      </c>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="T6" s="2">
+        <v>57.5</v>
+      </c>
+      <c r="V6" s="2">
+        <f t="shared" ref="V6:V49" si="0">L6*0.3+T6*0.7</f>
+        <v>60.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
         <v>28</v>
       </c>
@@ -1968,16 +2099,31 @@
         <v>30</v>
       </c>
       <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
+      <c r="E7" s="10">
+        <v>60</v>
+      </c>
+      <c r="F7" s="10">
+        <v>60</v>
+      </c>
+      <c r="G7" s="10">
+        <v>60</v>
+      </c>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-    </row>
-    <row r="8" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L7" s="30">
+        <v>60</v>
+      </c>
+      <c r="T7" s="2">
+        <v>62.5</v>
+      </c>
+      <c r="V7" s="2">
+        <f t="shared" si="0"/>
+        <v>61.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
         <v>31</v>
       </c>
@@ -1988,16 +2134,31 @@
         <v>33</v>
       </c>
       <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
+      <c r="E8" s="10">
+        <v>60</v>
+      </c>
+      <c r="F8" s="10">
+        <v>60</v>
+      </c>
+      <c r="G8" s="10">
+        <v>60</v>
+      </c>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-    </row>
-    <row r="9" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L8" s="30">
+        <v>60</v>
+      </c>
+      <c r="T8" s="2">
+        <v>67</v>
+      </c>
+      <c r="V8" s="2">
+        <f t="shared" si="0"/>
+        <v>64.900000000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
         <v>34</v>
       </c>
@@ -2008,16 +2169,43 @@
         <v>36</v>
       </c>
       <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
+      <c r="E9" s="10">
+        <v>60</v>
+      </c>
+      <c r="F9" s="10">
+        <v>60</v>
+      </c>
+      <c r="G9" s="10">
+        <v>60</v>
+      </c>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-    </row>
-    <row r="10" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L9" s="30">
+        <v>71</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="O9" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="P9" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="T9" s="2">
+        <v>55.5</v>
+      </c>
+      <c r="V9" s="2">
+        <f t="shared" si="0"/>
+        <v>60.149999999999991</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
@@ -2031,23 +2219,46 @@
       <c r="E10" s="10">
         <v>100</v>
       </c>
-      <c r="F10" s="10"/>
+      <c r="F10" s="10">
+        <v>100</v>
+      </c>
       <c r="G10" s="10">
-        <v>82</v>
-      </c>
-      <c r="H10" s="10">
+        <v>100</v>
+      </c>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10">
         <v>5</v>
       </c>
-      <c r="I10" s="10">
+      <c r="K10" s="10">
+        <v>5</v>
+      </c>
+      <c r="L10" s="30">
+        <v>100</v>
+      </c>
+      <c r="N10" s="2">
+        <f>E10*0.3+F10*0.5+G10*0.2+J10+K10</f>
+        <v>110</v>
+      </c>
+      <c r="O10" s="2">
+        <f>P10+Q10</f>
+        <v>138</v>
+      </c>
+      <c r="P10" s="2">
+        <v>89</v>
+      </c>
+      <c r="Q10" s="2">
         <v>49</v>
       </c>
-      <c r="J10" s="10">
-        <v>89</v>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T10" s="2">
+        <v>77</v>
+      </c>
+      <c r="V10" s="2">
+        <f t="shared" si="0"/>
+        <v>83.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
         <v>40</v>
       </c>
@@ -2061,49 +2272,92 @@
       <c r="E11" s="10">
         <v>73</v>
       </c>
-      <c r="F11" s="10"/>
+      <c r="F11" s="10">
+        <v>100</v>
+      </c>
       <c r="G11" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H11" s="10"/>
-      <c r="I11" s="10">
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="30">
+        <v>92</v>
+      </c>
+      <c r="N11" s="2">
+        <f t="shared" ref="N11:N49" si="1">E11*0.3+F11*0.5+G11*0.2+J11+K11</f>
+        <v>91.9</v>
+      </c>
+      <c r="O11" s="2">
+        <f t="shared" ref="O11:O49" si="2">P11+Q11</f>
+        <v>132</v>
+      </c>
+      <c r="P11" s="2">
+        <v>94</v>
+      </c>
+      <c r="Q11" s="2">
         <v>38</v>
       </c>
-      <c r="J11" s="10">
-        <v>94</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-    </row>
-    <row r="12" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T11" s="2">
+        <v>69.5</v>
+      </c>
+      <c r="V11" s="2">
+        <f t="shared" si="0"/>
+        <v>76.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="35" t="s">
         <v>44</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>45</v>
       </c>
       <c r="D12" s="10"/>
-      <c r="E12" s="10">
+      <c r="E12" s="29">
         <v>27</v>
       </c>
-      <c r="F12" s="10"/>
+      <c r="F12" s="10">
+        <v>70</v>
+      </c>
       <c r="G12" s="10">
         <v>82</v>
       </c>
       <c r="H12" s="10"/>
-      <c r="I12" s="10">
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="44">
+        <v>60</v>
+      </c>
+      <c r="M12" s="43"/>
+      <c r="N12" s="2">
+        <f t="shared" si="1"/>
+        <v>59.5</v>
+      </c>
+      <c r="O12" s="2">
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="J12" s="10">
+      <c r="P12" s="40">
         <v>0</v>
       </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-    </row>
-    <row r="13" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q12" s="2">
+        <v>24</v>
+      </c>
+      <c r="T12" s="2">
+        <v>72.5</v>
+      </c>
+      <c r="V12" s="2">
+        <f t="shared" si="0"/>
+        <v>68.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
         <v>46</v>
       </c>
@@ -2117,79 +2371,144 @@
       <c r="E13" s="10">
         <v>93</v>
       </c>
-      <c r="F13" s="10"/>
+      <c r="F13" s="10">
+        <v>100</v>
+      </c>
       <c r="G13" s="10">
-        <v>82</v>
-      </c>
-      <c r="H13" s="10">
+        <v>100</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10">
         <v>3</v>
       </c>
-      <c r="I13" s="10">
+      <c r="K13" s="10"/>
+      <c r="L13" s="30">
+        <v>100</v>
+      </c>
+      <c r="N13" s="2">
+        <f t="shared" si="1"/>
+        <v>100.9</v>
+      </c>
+      <c r="O13" s="2">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+      <c r="P13" s="2">
+        <v>96</v>
+      </c>
+      <c r="Q13" s="2">
         <v>49</v>
       </c>
-      <c r="J13" s="10">
-        <v>96</v>
-      </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-    </row>
-    <row r="14" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T13" s="2">
+        <v>73.5</v>
+      </c>
+      <c r="V13" s="2">
+        <f t="shared" si="0"/>
+        <v>81.449999999999989</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="34" t="s">
         <v>51</v>
       </c>
       <c r="D14" s="10"/>
-      <c r="E14" s="10">
+      <c r="E14" s="29">
         <v>20</v>
       </c>
-      <c r="F14" s="10"/>
+      <c r="F14" s="10">
+        <v>70</v>
+      </c>
       <c r="G14" s="10">
         <v>82</v>
       </c>
       <c r="H14" s="10"/>
-      <c r="I14" s="10">
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="44">
+        <v>57</v>
+      </c>
+      <c r="M14" s="43"/>
+      <c r="N14" s="2">
+        <f t="shared" si="1"/>
+        <v>57.400000000000006</v>
+      </c>
+      <c r="O14" s="2">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J14" s="52">
+      <c r="P14" s="40">
         <v>0</v>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-    </row>
-    <row r="15" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+      <c r="T14" s="33">
+        <v>35</v>
+      </c>
+      <c r="U14" s="33"/>
+      <c r="V14" s="2">
+        <f t="shared" si="0"/>
+        <v>41.599999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
         <v>52</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="46" t="s">
         <v>54</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10">
         <v>87</v>
       </c>
-      <c r="F15" s="10"/>
+      <c r="F15" s="10">
+        <v>98</v>
+      </c>
       <c r="G15" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H15" s="10"/>
-      <c r="I15" s="10">
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="30">
+        <v>95</v>
+      </c>
+      <c r="N15" s="2">
+        <f t="shared" si="1"/>
+        <v>95.1</v>
+      </c>
+      <c r="O15" s="2">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J15" s="52">
+      <c r="P15" s="39">
         <v>0</v>
       </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-    </row>
-    <row r="16" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q15" s="2">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2">
+        <v>45</v>
+      </c>
+      <c r="V15" s="2">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
         <v>55</v>
       </c>
@@ -2203,49 +2522,92 @@
       <c r="E16" s="10">
         <v>87</v>
       </c>
-      <c r="F16" s="10"/>
+      <c r="F16" s="10">
+        <v>78</v>
+      </c>
       <c r="G16" s="10">
+        <v>85</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="30">
         <v>82</v>
       </c>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10">
+      <c r="N16" s="2">
+        <f t="shared" si="1"/>
+        <v>82.1</v>
+      </c>
+      <c r="O16" s="2">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="P16" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q16" s="2">
         <v>2</v>
       </c>
-      <c r="J16" s="10">
-        <v>83</v>
-      </c>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-    </row>
-    <row r="17" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T16" s="2">
+        <v>52.5</v>
+      </c>
+      <c r="V16" s="2">
+        <f t="shared" si="0"/>
+        <v>61.349999999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="34" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10">
         <v>67</v>
       </c>
-      <c r="F17" s="10"/>
+      <c r="F17" s="10">
+        <v>80</v>
+      </c>
       <c r="G17" s="10">
         <v>82</v>
       </c>
       <c r="H17" s="10"/>
-      <c r="I17" s="10">
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="30">
+        <v>77</v>
+      </c>
+      <c r="N17" s="2">
+        <f t="shared" si="1"/>
+        <v>76.5</v>
+      </c>
+      <c r="O17" s="2">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="J17" s="10">
+      <c r="P17" s="2">
         <v>0</v>
       </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-    </row>
-    <row r="18" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q17" s="2">
+        <v>20</v>
+      </c>
+      <c r="T17" s="33">
+        <v>44</v>
+      </c>
+      <c r="U17" s="33"/>
+      <c r="V17" s="2">
+        <f t="shared" si="0"/>
+        <v>53.899999999999991</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
         <v>61</v>
       </c>
@@ -2259,21 +2621,42 @@
       <c r="E18" s="10">
         <v>80</v>
       </c>
-      <c r="F18" s="10"/>
+      <c r="F18" s="10">
+        <v>83</v>
+      </c>
       <c r="G18" s="10">
         <v>82</v>
       </c>
       <c r="H18" s="10"/>
-      <c r="I18" s="10">
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="30">
+        <v>82</v>
+      </c>
+      <c r="N18" s="2">
+        <f t="shared" si="1"/>
+        <v>81.900000000000006</v>
+      </c>
+      <c r="O18" s="2">
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="J18" s="52">
+      <c r="P18" s="2">
         <v>0</v>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q18" s="2">
+        <v>8</v>
+      </c>
+      <c r="T18" s="2">
+        <v>61.5</v>
+      </c>
+      <c r="V18" s="2">
+        <f t="shared" si="0"/>
+        <v>67.649999999999991</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="7" t="s">
         <v>64</v>
       </c>
@@ -2287,49 +2670,93 @@
       <c r="E19" s="10">
         <v>100</v>
       </c>
-      <c r="F19" s="10"/>
+      <c r="F19" s="10">
+        <v>100</v>
+      </c>
       <c r="G19" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H19" s="10"/>
-      <c r="I19" s="10">
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10">
+        <v>5</v>
+      </c>
+      <c r="L19" s="30">
+        <v>100</v>
+      </c>
+      <c r="N19" s="2">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="O19" s="2">
+        <f t="shared" si="2"/>
+        <v>143</v>
+      </c>
+      <c r="P19" s="2">
+        <v>97</v>
+      </c>
+      <c r="Q19" s="2">
         <v>46</v>
       </c>
-      <c r="J19" s="10">
-        <v>97</v>
-      </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-    </row>
-    <row r="20" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T19" s="2">
+        <v>62.5</v>
+      </c>
+      <c r="V19" s="2">
+        <f t="shared" si="0"/>
+        <v>73.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="36" t="s">
         <v>69</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10">
         <v>47</v>
       </c>
-      <c r="F20" s="10"/>
+      <c r="F20" s="10">
+        <v>88</v>
+      </c>
       <c r="G20" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H20" s="10"/>
-      <c r="I20" s="10">
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="30">
+        <v>78</v>
+      </c>
+      <c r="N20" s="2">
+        <f t="shared" si="1"/>
+        <v>78.099999999999994</v>
+      </c>
+      <c r="O20" s="2">
+        <f t="shared" si="2"/>
+        <v>101</v>
+      </c>
+      <c r="P20" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="2">
         <v>28</v>
       </c>
-      <c r="J20" s="10">
-        <v>73</v>
-      </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-    </row>
-    <row r="21" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T20" s="2">
+        <v>65.5</v>
+      </c>
+      <c r="V20" s="2">
+        <f t="shared" si="0"/>
+        <v>69.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7" t="s">
         <v>70</v>
       </c>
@@ -2343,21 +2770,42 @@
       <c r="E21" s="10">
         <v>87</v>
       </c>
-      <c r="F21" s="10"/>
+      <c r="F21" s="10">
+        <v>100</v>
+      </c>
       <c r="G21" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H21" s="10"/>
-      <c r="I21" s="10">
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="30">
+        <v>96</v>
+      </c>
+      <c r="N21" s="2">
+        <f t="shared" si="1"/>
+        <v>96.1</v>
+      </c>
+      <c r="O21" s="2">
+        <f t="shared" si="2"/>
+        <v>116</v>
+      </c>
+      <c r="P21" s="2">
+        <v>92</v>
+      </c>
+      <c r="Q21" s="2">
         <v>24</v>
       </c>
-      <c r="J21" s="10">
-        <v>92</v>
-      </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-    </row>
-    <row r="22" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T21" s="2">
+        <v>80.5</v>
+      </c>
+      <c r="V21" s="2">
+        <f t="shared" si="0"/>
+        <v>85.149999999999991</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="7" t="s">
         <v>73</v>
       </c>
@@ -2371,21 +2819,42 @@
       <c r="E22" s="10">
         <v>93</v>
       </c>
-      <c r="F22" s="10"/>
+      <c r="F22" s="10">
+        <v>100</v>
+      </c>
       <c r="G22" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H22" s="10"/>
-      <c r="I22" s="10">
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="30">
+        <v>98</v>
+      </c>
+      <c r="N22" s="2">
+        <f t="shared" si="1"/>
+        <v>97.9</v>
+      </c>
+      <c r="O22" s="2">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="P22" s="2">
+        <v>86</v>
+      </c>
+      <c r="Q22" s="2">
         <v>34</v>
       </c>
-      <c r="J22" s="10">
-        <v>86</v>
-      </c>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-    </row>
-    <row r="23" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T22" s="2">
+        <v>80.5</v>
+      </c>
+      <c r="V22" s="2">
+        <f t="shared" si="0"/>
+        <v>85.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="7" t="s">
         <v>76</v>
       </c>
@@ -2399,21 +2868,44 @@
       <c r="E23" s="10">
         <v>100</v>
       </c>
-      <c r="F23" s="10"/>
+      <c r="F23" s="10">
+        <v>86</v>
+      </c>
       <c r="G23" s="10">
         <v>82</v>
       </c>
       <c r="H23" s="10"/>
-      <c r="I23" s="10">
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10">
+        <v>5</v>
+      </c>
+      <c r="L23" s="30">
+        <v>94</v>
+      </c>
+      <c r="N23" s="2">
+        <f t="shared" si="1"/>
+        <v>94.4</v>
+      </c>
+      <c r="O23" s="2">
+        <f t="shared" si="2"/>
         <v>56</v>
       </c>
-      <c r="J23" s="10">
+      <c r="P23" s="2">
         <v>0</v>
       </c>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-    </row>
-    <row r="24" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q23" s="2">
+        <v>56</v>
+      </c>
+      <c r="T23" s="2">
+        <v>56</v>
+      </c>
+      <c r="V23" s="2">
+        <f t="shared" si="0"/>
+        <v>67.399999999999991</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="7" t="s">
         <v>79</v>
       </c>
@@ -2427,21 +2919,42 @@
       <c r="E24" s="10">
         <v>93</v>
       </c>
-      <c r="F24" s="10"/>
+      <c r="F24" s="10">
+        <v>88</v>
+      </c>
       <c r="G24" s="10">
         <v>82</v>
       </c>
       <c r="H24" s="10"/>
-      <c r="I24" s="10">
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="30">
+        <v>88</v>
+      </c>
+      <c r="N24" s="2">
+        <f t="shared" si="1"/>
+        <v>88.300000000000011</v>
+      </c>
+      <c r="O24" s="2">
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="J24" s="52">
+      <c r="P24" s="2">
         <v>0</v>
       </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-    </row>
-    <row r="25" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q24" s="2">
+        <v>48</v>
+      </c>
+      <c r="T24" s="2">
+        <v>66</v>
+      </c>
+      <c r="V24" s="2">
+        <f t="shared" si="0"/>
+        <v>72.599999999999994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="7" t="s">
         <v>82</v>
       </c>
@@ -2455,21 +2968,42 @@
       <c r="E25" s="10">
         <v>93</v>
       </c>
-      <c r="F25" s="10"/>
+      <c r="F25" s="10">
+        <v>100</v>
+      </c>
       <c r="G25" s="10">
+        <v>100</v>
+      </c>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="30">
+        <v>98</v>
+      </c>
+      <c r="N25" s="2">
+        <f t="shared" si="1"/>
+        <v>97.9</v>
+      </c>
+      <c r="O25" s="2">
+        <f t="shared" si="2"/>
+        <v>130</v>
+      </c>
+      <c r="P25" s="2">
         <v>82</v>
       </c>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10">
+      <c r="Q25" s="2">
         <v>48</v>
       </c>
-      <c r="J25" s="10">
-        <v>82</v>
-      </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-    </row>
-    <row r="26" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T25" s="2">
+        <v>73</v>
+      </c>
+      <c r="V25" s="2">
+        <f t="shared" si="0"/>
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="7" t="s">
         <v>85</v>
       </c>
@@ -2483,51 +3017,94 @@
       <c r="E26" s="10">
         <v>80</v>
       </c>
-      <c r="F26" s="10"/>
+      <c r="F26" s="10">
+        <v>100</v>
+      </c>
       <c r="G26" s="10">
-        <v>82</v>
-      </c>
-      <c r="H26" s="10">
+        <v>100</v>
+      </c>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10">
         <v>3</v>
       </c>
-      <c r="I26" s="10">
+      <c r="K26" s="10"/>
+      <c r="L26" s="30">
+        <v>97</v>
+      </c>
+      <c r="N26" s="2">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="O26" s="2">
+        <f t="shared" si="2"/>
+        <v>118</v>
+      </c>
+      <c r="P26" s="2">
+        <v>100</v>
+      </c>
+      <c r="Q26" s="2">
         <v>18</v>
       </c>
-      <c r="J26" s="10">
-        <v>100</v>
-      </c>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-    </row>
-    <row r="27" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T26" s="2">
+        <v>92</v>
+      </c>
+      <c r="V26" s="2">
+        <f t="shared" si="0"/>
+        <v>93.499999999999986</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="35" t="s">
         <v>89</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>90</v>
       </c>
       <c r="D27" s="10"/>
-      <c r="E27" s="10">
+      <c r="E27" s="29">
         <v>47</v>
       </c>
-      <c r="F27" s="10"/>
+      <c r="F27" s="10">
+        <v>98</v>
+      </c>
       <c r="G27" s="10">
+        <v>95</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="44">
         <v>82</v>
       </c>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10">
+      <c r="M27" s="43"/>
+      <c r="N27" s="2">
+        <f t="shared" si="1"/>
+        <v>82.1</v>
+      </c>
+      <c r="O27" s="2">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="P27" s="40">
+        <v>95</v>
+      </c>
+      <c r="Q27" s="2">
         <v>0</v>
       </c>
-      <c r="J27" s="10">
-        <v>95</v>
-      </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-    </row>
-    <row r="28" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T27" s="2">
+        <v>60.5</v>
+      </c>
+      <c r="V27" s="2">
+        <f t="shared" si="0"/>
+        <v>66.949999999999989</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="7" t="s">
         <v>91</v>
       </c>
@@ -2541,51 +3118,93 @@
       <c r="E28" s="10">
         <v>93</v>
       </c>
-      <c r="F28" s="10"/>
+      <c r="F28" s="10">
+        <v>83</v>
+      </c>
       <c r="G28" s="10">
         <v>82</v>
       </c>
       <c r="H28" s="10"/>
-      <c r="I28" s="10">
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="30">
+        <v>86</v>
+      </c>
+      <c r="N28" s="2">
+        <f t="shared" si="1"/>
+        <v>85.800000000000011</v>
+      </c>
+      <c r="O28" s="2">
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="J28" s="52">
+      <c r="P28" s="2">
         <v>0</v>
       </c>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-    </row>
-    <row r="29" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q28" s="2">
+        <v>24</v>
+      </c>
+      <c r="T28" s="2">
+        <v>71.5</v>
+      </c>
+      <c r="V28" s="2">
+        <f t="shared" si="0"/>
+        <v>75.849999999999994</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="7" t="s">
         <v>94</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="36" t="s">
         <v>96</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10">
         <v>67</v>
       </c>
-      <c r="F29" s="10"/>
+      <c r="F29" s="10">
+        <v>87</v>
+      </c>
       <c r="G29" s="10">
         <v>82</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10">
         <v>4</v>
       </c>
-      <c r="I29" s="10">
+      <c r="K29" s="10"/>
+      <c r="L29" s="30">
+        <v>84</v>
+      </c>
+      <c r="N29" s="2">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="O29" s="2">
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="J29" s="52">
+      <c r="P29" s="2">
         <v>0</v>
       </c>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-    </row>
-    <row r="30" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q29" s="2">
+        <v>18</v>
+      </c>
+      <c r="T29" s="2">
+        <v>93.5</v>
+      </c>
+      <c r="V29" s="2">
+        <f t="shared" si="0"/>
+        <v>90.65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="7" t="s">
         <v>97</v>
       </c>
@@ -2599,49 +3218,93 @@
       <c r="E30" s="10">
         <v>73</v>
       </c>
-      <c r="F30" s="10"/>
+      <c r="F30" s="10">
+        <v>83</v>
+      </c>
       <c r="G30" s="10">
         <v>82</v>
       </c>
       <c r="H30" s="10"/>
-      <c r="I30" s="10">
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="30">
+        <v>80</v>
+      </c>
+      <c r="N30" s="2">
+        <f t="shared" si="1"/>
+        <v>79.8</v>
+      </c>
+      <c r="O30" s="2">
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="J30" s="10">
+      <c r="P30" s="2">
         <v>0</v>
       </c>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-    </row>
-    <row r="31" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q30" s="2">
+        <v>31</v>
+      </c>
+      <c r="T30" s="33">
+        <v>38</v>
+      </c>
+      <c r="U30" s="33"/>
+      <c r="V30" s="2">
+        <f t="shared" si="0"/>
+        <v>50.599999999999994</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="7" t="s">
         <v>100</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="34" t="s">
         <v>102</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10">
         <v>93</v>
       </c>
-      <c r="F31" s="10"/>
+      <c r="F31" s="10">
+        <v>80</v>
+      </c>
       <c r="G31" s="10">
         <v>82</v>
       </c>
       <c r="H31" s="10"/>
-      <c r="I31" s="10">
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="30">
+        <v>84</v>
+      </c>
+      <c r="N31" s="2">
+        <f t="shared" si="1"/>
+        <v>84.300000000000011</v>
+      </c>
+      <c r="O31" s="2">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J31" s="52">
+      <c r="P31" s="2">
         <v>0</v>
       </c>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-    </row>
-    <row r="32" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q31" s="2">
+        <v>0</v>
+      </c>
+      <c r="T31" s="33">
+        <v>41</v>
+      </c>
+      <c r="U31" s="33"/>
+      <c r="V31" s="2">
+        <f t="shared" si="0"/>
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7" t="s">
         <v>103</v>
       </c>
@@ -2655,77 +3318,143 @@
       <c r="E32" s="10">
         <v>93</v>
       </c>
-      <c r="F32" s="10"/>
+      <c r="F32" s="10">
+        <v>99</v>
+      </c>
       <c r="G32" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H32" s="10"/>
-      <c r="I32" s="10">
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="30">
+        <v>97</v>
+      </c>
+      <c r="N32" s="2">
+        <f t="shared" si="1"/>
+        <v>97.4</v>
+      </c>
+      <c r="O32" s="2">
+        <f t="shared" si="2"/>
+        <v>129</v>
+      </c>
+      <c r="P32" s="2">
+        <v>93</v>
+      </c>
+      <c r="Q32" s="2">
         <v>36</v>
       </c>
-      <c r="J32" s="10">
-        <v>93</v>
-      </c>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-    </row>
-    <row r="33" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T32" s="2">
+        <v>64</v>
+      </c>
+      <c r="V32" s="2">
+        <f t="shared" si="0"/>
+        <v>73.899999999999991</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="7" t="s">
         <v>106</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="46" t="s">
         <v>108</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10">
         <v>87</v>
       </c>
-      <c r="F33" s="10"/>
+      <c r="F33" s="10">
+        <v>80</v>
+      </c>
       <c r="G33" s="10">
         <v>82</v>
       </c>
       <c r="H33" s="10"/>
-      <c r="I33" s="10">
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="48">
+        <v>83</v>
+      </c>
+      <c r="M33" s="50"/>
+      <c r="N33" s="2">
+        <f t="shared" si="1"/>
+        <v>82.5</v>
+      </c>
+      <c r="O33" s="2">
+        <f t="shared" si="2"/>
         <v>44</v>
       </c>
-      <c r="J33" s="52">
+      <c r="P33" s="2">
         <v>0</v>
       </c>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-    </row>
-    <row r="34" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q33" s="2">
+        <v>44</v>
+      </c>
+      <c r="T33" s="33">
+        <v>45</v>
+      </c>
+      <c r="U33" s="33"/>
+      <c r="V33" s="2">
+        <f t="shared" si="0"/>
+        <v>56.399999999999991</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="7" t="s">
         <v>109</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="34" t="s">
         <v>111</v>
       </c>
       <c r="D34" s="10"/>
-      <c r="E34" s="10">
+      <c r="E34" s="29">
         <v>60</v>
       </c>
-      <c r="F34" s="10"/>
+      <c r="F34" s="10">
+        <v>92</v>
+      </c>
       <c r="G34" s="10">
         <v>82</v>
       </c>
       <c r="H34" s="10"/>
-      <c r="I34" s="10">
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="30">
+        <v>80</v>
+      </c>
+      <c r="N34" s="2">
+        <f t="shared" si="1"/>
+        <v>80.400000000000006</v>
+      </c>
+      <c r="O34" s="2">
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="J34" s="10">
+      <c r="P34" s="2">
         <v>0</v>
       </c>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-    </row>
-    <row r="35" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q34" s="2">
+        <v>32</v>
+      </c>
+      <c r="T34" s="33">
+        <v>44.5</v>
+      </c>
+      <c r="U34" s="33"/>
+      <c r="V34" s="2">
+        <f t="shared" si="0"/>
+        <v>55.15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="7" t="s">
         <v>112</v>
       </c>
@@ -2739,23 +3468,46 @@
       <c r="E35" s="10">
         <v>100</v>
       </c>
-      <c r="F35" s="10"/>
+      <c r="F35" s="10">
+        <v>100</v>
+      </c>
       <c r="G35" s="10">
-        <v>82</v>
-      </c>
-      <c r="H35" s="10">
+        <v>100</v>
+      </c>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10">
         <v>1</v>
       </c>
-      <c r="I35" s="10">
+      <c r="K35" s="10">
+        <v>5</v>
+      </c>
+      <c r="L35" s="30">
+        <v>100</v>
+      </c>
+      <c r="N35" s="2">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="O35" s="2">
+        <f t="shared" si="2"/>
+        <v>142</v>
+      </c>
+      <c r="P35" s="2">
+        <v>100</v>
+      </c>
+      <c r="Q35" s="2">
         <v>42</v>
       </c>
-      <c r="J35" s="10">
-        <v>100</v>
-      </c>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-    </row>
-    <row r="36" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T35" s="2">
+        <v>60.5</v>
+      </c>
+      <c r="V35" s="2">
+        <f t="shared" si="0"/>
+        <v>72.349999999999994</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="7" t="s">
         <v>115</v>
       </c>
@@ -2769,49 +3521,93 @@
       <c r="E36" s="10">
         <v>67</v>
       </c>
-      <c r="F36" s="10"/>
+      <c r="F36" s="10">
+        <v>97</v>
+      </c>
       <c r="G36" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H36" s="10"/>
-      <c r="I36" s="10">
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="30">
+        <v>89</v>
+      </c>
+      <c r="N36" s="2">
+        <f t="shared" si="1"/>
+        <v>88.6</v>
+      </c>
+      <c r="O36" s="2">
+        <f t="shared" si="2"/>
+        <v>117</v>
+      </c>
+      <c r="P36" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q36" s="2">
         <v>32</v>
       </c>
-      <c r="J36" s="10">
-        <v>85</v>
-      </c>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-    </row>
-    <row r="37" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T36" s="33">
+        <v>29.5</v>
+      </c>
+      <c r="U36" s="33"/>
+      <c r="V36" s="2">
+        <f t="shared" si="0"/>
+        <v>47.349999999999994</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B37" s="30" t="s">
+      <c r="B37" s="35" t="s">
         <v>119</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D37" s="10"/>
-      <c r="E37" s="10">
+      <c r="E37" s="29">
         <v>47</v>
       </c>
-      <c r="F37" s="10"/>
+      <c r="F37" s="10">
+        <v>83</v>
+      </c>
       <c r="G37" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H37" s="10"/>
-      <c r="I37" s="10">
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="44">
+        <v>76</v>
+      </c>
+      <c r="M37" s="43"/>
+      <c r="N37" s="2">
+        <f t="shared" si="1"/>
+        <v>75.599999999999994</v>
+      </c>
+      <c r="O37" s="2">
+        <f t="shared" si="2"/>
+        <v>103</v>
+      </c>
+      <c r="P37" s="40">
+        <v>95</v>
+      </c>
+      <c r="Q37" s="2">
         <v>8</v>
       </c>
-      <c r="J37" s="10">
-        <v>95</v>
-      </c>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-    </row>
-    <row r="38" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T37" s="2">
+        <v>60</v>
+      </c>
+      <c r="V37" s="2">
+        <f t="shared" si="0"/>
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="7" t="s">
         <v>121</v>
       </c>
@@ -2825,21 +3621,42 @@
       <c r="E38" s="10">
         <v>93</v>
       </c>
-      <c r="F38" s="10"/>
+      <c r="F38" s="10">
+        <v>80</v>
+      </c>
       <c r="G38" s="10">
         <v>82</v>
       </c>
       <c r="H38" s="10"/>
-      <c r="I38" s="10">
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="30">
+        <v>84</v>
+      </c>
+      <c r="N38" s="2">
+        <f t="shared" si="1"/>
+        <v>84.300000000000011</v>
+      </c>
+      <c r="O38" s="2">
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="J38" s="52">
+      <c r="P38" s="2">
         <v>0</v>
       </c>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-    </row>
-    <row r="39" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q38" s="2">
+        <v>12</v>
+      </c>
+      <c r="T38" s="2">
+        <v>61.5</v>
+      </c>
+      <c r="V38" s="2">
+        <f t="shared" si="0"/>
+        <v>68.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="7" t="s">
         <v>124</v>
       </c>
@@ -2853,23 +3670,46 @@
       <c r="E39" s="10">
         <v>100</v>
       </c>
-      <c r="F39" s="10"/>
+      <c r="F39" s="10">
+        <v>100</v>
+      </c>
       <c r="G39" s="10">
-        <v>82</v>
-      </c>
-      <c r="H39" s="10">
+        <v>100</v>
+      </c>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10">
         <v>4</v>
       </c>
-      <c r="I39" s="10">
+      <c r="K39" s="10">
+        <v>5</v>
+      </c>
+      <c r="L39" s="30">
+        <v>100</v>
+      </c>
+      <c r="N39" s="2">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="O39" s="2">
+        <f t="shared" si="2"/>
+        <v>147</v>
+      </c>
+      <c r="P39" s="2">
+        <v>91</v>
+      </c>
+      <c r="Q39" s="2">
         <v>56</v>
       </c>
-      <c r="J39" s="10">
-        <v>91</v>
-      </c>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-    </row>
-    <row r="40" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T39" s="2">
+        <v>80</v>
+      </c>
+      <c r="V39" s="2">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="7" t="s">
         <v>127</v>
       </c>
@@ -2883,23 +3723,46 @@
       <c r="E40" s="10">
         <v>100</v>
       </c>
-      <c r="F40" s="10"/>
+      <c r="F40" s="10">
+        <v>83</v>
+      </c>
       <c r="G40" s="10">
-        <v>82</v>
-      </c>
-      <c r="H40" s="10">
+        <v>100</v>
+      </c>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10">
         <v>2</v>
       </c>
-      <c r="I40" s="10">
+      <c r="K40" s="10">
+        <v>5</v>
+      </c>
+      <c r="L40" s="30">
+        <v>99</v>
+      </c>
+      <c r="N40" s="2">
+        <f t="shared" si="1"/>
+        <v>98.5</v>
+      </c>
+      <c r="O40" s="2">
+        <f t="shared" si="2"/>
+        <v>101</v>
+      </c>
+      <c r="P40" s="2">
+        <v>97</v>
+      </c>
+      <c r="Q40" s="2">
         <v>4</v>
       </c>
-      <c r="J40" s="10">
-        <v>97</v>
-      </c>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-    </row>
-    <row r="41" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T40" s="2">
+        <v>77.5</v>
+      </c>
+      <c r="V40" s="2">
+        <f t="shared" si="0"/>
+        <v>83.95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="7" t="s">
         <v>130</v>
       </c>
@@ -2913,21 +3776,44 @@
       <c r="E41" s="10">
         <v>100</v>
       </c>
-      <c r="F41" s="10"/>
+      <c r="F41" s="10">
+        <v>100</v>
+      </c>
       <c r="G41" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H41" s="10"/>
-      <c r="I41" s="10">
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10">
+        <v>5</v>
+      </c>
+      <c r="L41" s="30">
+        <v>100</v>
+      </c>
+      <c r="N41" s="2">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="O41" s="2">
+        <f t="shared" si="2"/>
+        <v>137</v>
+      </c>
+      <c r="P41" s="2">
+        <v>89</v>
+      </c>
+      <c r="Q41" s="2">
         <v>48</v>
       </c>
-      <c r="J41" s="10">
-        <v>89</v>
-      </c>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-    </row>
-    <row r="42" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T41" s="2">
+        <v>79</v>
+      </c>
+      <c r="V41" s="2">
+        <f t="shared" si="0"/>
+        <v>85.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="7" t="s">
         <v>133</v>
       </c>
@@ -2941,21 +3827,42 @@
       <c r="E42" s="10">
         <v>93</v>
       </c>
-      <c r="F42" s="10"/>
+      <c r="F42" s="10">
+        <v>100</v>
+      </c>
       <c r="G42" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H42" s="10"/>
-      <c r="I42" s="10">
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="30">
+        <v>98</v>
+      </c>
+      <c r="N42" s="2">
+        <f t="shared" si="1"/>
+        <v>97.9</v>
+      </c>
+      <c r="O42" s="2">
+        <f t="shared" si="2"/>
+        <v>147</v>
+      </c>
+      <c r="P42" s="2">
+        <v>94</v>
+      </c>
+      <c r="Q42" s="2">
         <v>53</v>
       </c>
-      <c r="J42" s="10">
-        <v>94</v>
-      </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-    </row>
-    <row r="43" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T42" s="2">
+        <v>84.5</v>
+      </c>
+      <c r="V42" s="2">
+        <f t="shared" si="0"/>
+        <v>88.55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="7" t="s">
         <v>136</v>
       </c>
@@ -2969,23 +3876,46 @@
       <c r="E43" s="10">
         <v>100</v>
       </c>
-      <c r="F43" s="10"/>
+      <c r="F43" s="10">
+        <v>100</v>
+      </c>
       <c r="G43" s="10">
-        <v>82</v>
-      </c>
-      <c r="H43" s="10">
+        <v>100</v>
+      </c>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10">
         <v>3</v>
       </c>
-      <c r="I43" s="10">
+      <c r="K43" s="10">
+        <v>5</v>
+      </c>
+      <c r="L43" s="30">
+        <v>100</v>
+      </c>
+      <c r="N43" s="2">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="O43" s="2">
+        <f t="shared" si="2"/>
+        <v>128</v>
+      </c>
+      <c r="P43" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q43" s="2">
         <v>50</v>
       </c>
-      <c r="J43" s="10">
-        <v>78</v>
-      </c>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-    </row>
-    <row r="44" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T43" s="2">
+        <v>74</v>
+      </c>
+      <c r="V43" s="2">
+        <f t="shared" si="0"/>
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="7" t="s">
         <v>139</v>
       </c>
@@ -2999,23 +3929,46 @@
       <c r="E44" s="10">
         <v>100</v>
       </c>
-      <c r="F44" s="10"/>
+      <c r="F44" s="10">
+        <v>85</v>
+      </c>
       <c r="G44" s="10">
         <v>82</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10">
         <v>3</v>
       </c>
-      <c r="I44" s="10">
+      <c r="K44" s="10">
+        <v>5</v>
+      </c>
+      <c r="L44" s="30">
+        <v>97</v>
+      </c>
+      <c r="N44" s="2">
+        <f t="shared" si="1"/>
+        <v>96.9</v>
+      </c>
+      <c r="O44" s="2">
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="J44" s="10">
+      <c r="P44" s="2">
         <v>0</v>
       </c>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-    </row>
-    <row r="45" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q44" s="2">
+        <v>60</v>
+      </c>
+      <c r="T44" s="2">
+        <v>61</v>
+      </c>
+      <c r="V44" s="2">
+        <f t="shared" si="0"/>
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="7" t="s">
         <v>142</v>
       </c>
@@ -3029,23 +3982,46 @@
       <c r="E45" s="10">
         <v>100</v>
       </c>
-      <c r="F45" s="10"/>
+      <c r="F45" s="10">
+        <v>100</v>
+      </c>
       <c r="G45" s="10">
-        <v>82</v>
-      </c>
-      <c r="H45" s="10">
+        <v>100</v>
+      </c>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10">
         <v>2</v>
       </c>
-      <c r="I45" s="10">
+      <c r="K45" s="10">
+        <v>5</v>
+      </c>
+      <c r="L45" s="30">
+        <v>100</v>
+      </c>
+      <c r="N45" s="2">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="O45" s="2">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+      <c r="P45" s="2">
+        <v>86</v>
+      </c>
+      <c r="Q45" s="2">
         <v>54</v>
       </c>
-      <c r="J45" s="10">
-        <v>86</v>
-      </c>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-    </row>
-    <row r="46" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T45" s="2">
+        <v>61</v>
+      </c>
+      <c r="V45" s="2">
+        <f t="shared" si="0"/>
+        <v>72.699999999999989</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7" t="s">
         <v>145</v>
       </c>
@@ -3059,23 +4035,44 @@
       <c r="E46" s="10">
         <v>93</v>
       </c>
-      <c r="F46" s="10"/>
+      <c r="F46" s="10">
+        <v>90</v>
+      </c>
       <c r="G46" s="10">
         <v>82</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10">
         <v>3</v>
       </c>
-      <c r="I46" s="10">
+      <c r="K46" s="10"/>
+      <c r="L46" s="30">
+        <v>92</v>
+      </c>
+      <c r="N46" s="2">
+        <f t="shared" si="1"/>
+        <v>92.300000000000011</v>
+      </c>
+      <c r="O46" s="2">
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="J46" s="10">
+      <c r="P46" s="2">
         <v>0</v>
       </c>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-    </row>
-    <row r="47" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q46" s="2">
+        <v>48</v>
+      </c>
+      <c r="T46" s="2">
+        <v>60.5</v>
+      </c>
+      <c r="V46" s="2">
+        <f t="shared" si="0"/>
+        <v>69.949999999999989</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="7" t="s">
         <v>148</v>
       </c>
@@ -3089,23 +4086,46 @@
       <c r="E47" s="10">
         <v>100</v>
       </c>
-      <c r="F47" s="10"/>
+      <c r="F47" s="10">
+        <v>100</v>
+      </c>
       <c r="G47" s="10">
-        <v>82</v>
-      </c>
-      <c r="H47" s="10">
+        <v>100</v>
+      </c>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10">
         <v>10</v>
       </c>
-      <c r="I47" s="10">
+      <c r="K47" s="10">
+        <v>5</v>
+      </c>
+      <c r="L47" s="30">
+        <v>100</v>
+      </c>
+      <c r="N47" s="2">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="O47" s="2">
+        <f t="shared" si="2"/>
+        <v>157</v>
+      </c>
+      <c r="P47" s="2">
+        <v>99</v>
+      </c>
+      <c r="Q47" s="2">
         <v>58</v>
       </c>
-      <c r="J47" s="10">
-        <v>99</v>
-      </c>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-    </row>
-    <row r="48" spans="1:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T47" s="2">
+        <v>93</v>
+      </c>
+      <c r="V47" s="2">
+        <f t="shared" si="0"/>
+        <v>95.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="7" t="s">
         <v>151</v>
       </c>
@@ -3119,142 +4139,222 @@
       <c r="E48" s="10">
         <v>87</v>
       </c>
-      <c r="F48" s="10"/>
+      <c r="F48" s="10">
+        <v>100</v>
+      </c>
       <c r="G48" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H48" s="10"/>
-      <c r="I48" s="10">
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="30">
+        <v>96</v>
+      </c>
+      <c r="N48" s="2">
+        <f t="shared" si="1"/>
+        <v>96.1</v>
+      </c>
+      <c r="O48" s="2">
+        <f t="shared" si="2"/>
+        <v>155</v>
+      </c>
+      <c r="P48" s="2">
+        <v>95</v>
+      </c>
+      <c r="Q48" s="2">
         <v>60</v>
       </c>
-      <c r="J48" s="10">
-        <v>95</v>
-      </c>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-    </row>
-    <row r="49" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T48" s="2">
+        <v>70.5</v>
+      </c>
+      <c r="V48" s="2">
+        <f t="shared" si="0"/>
+        <v>78.149999999999991</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="7" t="s">
         <v>154</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="36" t="s">
         <v>156</v>
       </c>
       <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
+      <c r="E49" s="10">
+        <v>60</v>
+      </c>
+      <c r="F49" s="10">
+        <v>100</v>
+      </c>
+      <c r="G49" s="10">
+        <v>100</v>
+      </c>
       <c r="H49" s="10"/>
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-    </row>
-    <row r="50" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="47" t="s">
+      <c r="L49" s="30">
+        <v>88</v>
+      </c>
+      <c r="N49" s="2">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="O49" s="2">
+        <f t="shared" si="2"/>
+        <v>134</v>
+      </c>
+      <c r="P49" s="2">
+        <v>94</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>40</v>
+      </c>
+      <c r="T49" s="2">
+        <v>79</v>
+      </c>
+      <c r="V49" s="2">
+        <f t="shared" si="0"/>
+        <v>81.699999999999989</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R50" s="2"/>
+      <c r="S50" s="2"/>
+      <c r="V50" s="2"/>
+    </row>
+    <row r="51" spans="1:22" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="47"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="47"/>
-      <c r="I51" s="47"/>
-      <c r="J51" s="47"/>
-      <c r="K51" s="47"/>
-      <c r="L51" s="47"/>
-      <c r="M51" s="47"/>
-    </row>
-    <row r="52" spans="1:13" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="48" t="s">
+      <c r="B51" s="55"/>
+      <c r="C51" s="55"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="55"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="55"/>
+      <c r="J51" s="55"/>
+      <c r="K51" s="55"/>
+      <c r="L51" s="55"/>
+      <c r="M51" s="55"/>
+      <c r="N51" s="55"/>
+      <c r="O51" s="55"/>
+      <c r="P51" s="55"/>
+      <c r="Q51" s="55"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="2"/>
+      <c r="V51" s="2"/>
+    </row>
+    <row r="52" spans="1:22" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="B52" s="48"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="49" t="s">
+      <c r="B52" s="56"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E52" s="49"/>
-      <c r="F52" s="49"/>
-      <c r="G52" s="49" t="s">
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="H52" s="49"/>
-      <c r="I52" s="49"/>
-      <c r="J52" s="49" t="s">
+      <c r="H52" s="57"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="K52" s="49"/>
-      <c r="L52" s="49"/>
-      <c r="M52" s="19"/>
-    </row>
-    <row r="53" spans="1:13" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="44" t="s">
+      <c r="K52" s="57"/>
+      <c r="L52" s="57"/>
+      <c r="M52" s="31"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="31"/>
+      <c r="Q52" s="19"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="2"/>
+      <c r="V52" s="2"/>
+    </row>
+    <row r="53" spans="1:22" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B53" s="45" t="s">
+      <c r="B53" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="46" t="s">
+      <c r="C53" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="D53" s="43" t="s">
+      <c r="D53" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="E53" s="43"/>
-      <c r="F53" s="43"/>
-      <c r="G53" s="43"/>
-      <c r="H53" s="43"/>
-      <c r="I53" s="43"/>
-      <c r="J53" s="43"/>
-      <c r="K53" s="43"/>
-      <c r="L53" s="37" t="s">
+      <c r="E53" s="59"/>
+      <c r="F53" s="59"/>
+      <c r="G53" s="59"/>
+      <c r="H53" s="59"/>
+      <c r="I53" s="59"/>
+      <c r="J53" s="59"/>
+      <c r="K53" s="59"/>
+      <c r="L53" s="58" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="44"/>
-      <c r="B54" s="45"/>
-      <c r="C54" s="46"/>
-      <c r="D54" s="32" t="s">
+      <c r="M53" s="38"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="38"/>
+      <c r="P53" s="38"/>
+    </row>
+    <row r="54" spans="1:22" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="54"/>
+      <c r="B54" s="60"/>
+      <c r="C54" s="61"/>
+      <c r="D54" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E54" s="32" t="s">
+      <c r="E54" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="F54" s="32" t="s">
+      <c r="F54" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="G54" s="32" t="s">
+      <c r="G54" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H54" s="32"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="32"/>
-      <c r="K54" s="32"/>
-      <c r="L54" s="37"/>
-    </row>
-    <row r="55" spans="1:13" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="44"/>
-      <c r="B55" s="45"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="32"/>
-      <c r="L55" s="37"/>
-    </row>
-    <row r="56" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H54" s="52"/>
+      <c r="I54" s="52"/>
+      <c r="J54" s="52"/>
+      <c r="K54" s="52"/>
+      <c r="L54" s="58"/>
+      <c r="M54" s="38"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="38"/>
+      <c r="P54" s="38"/>
+    </row>
+    <row r="55" spans="1:22" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="54"/>
+      <c r="B55" s="60"/>
+      <c r="C55" s="61"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="52"/>
+      <c r="F55" s="52"/>
+      <c r="G55" s="52"/>
+      <c r="H55" s="52"/>
+      <c r="I55" s="52"/>
+      <c r="J55" s="52"/>
+      <c r="K55" s="52"/>
+      <c r="L55" s="58"/>
+      <c r="M55" s="38"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="38"/>
+      <c r="P55" s="38"/>
+    </row>
+    <row r="56" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="7" t="s">
         <v>157</v>
       </c>
@@ -3268,74 +4368,121 @@
       <c r="E56" s="10">
         <v>93</v>
       </c>
-      <c r="F56" s="10"/>
+      <c r="F56" s="10">
+        <v>86</v>
+      </c>
       <c r="G56" s="10">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H56" s="10"/>
-      <c r="I56" s="10">
-        <v>40</v>
-      </c>
-      <c r="J56" s="10">
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10">
+        <v>91</v>
+      </c>
+      <c r="N56" s="2">
+        <f>E56*0.3+F56*0.5+G56*0.2+J56+K56</f>
+        <v>90.9</v>
+      </c>
+      <c r="O56" s="2">
+        <f>P56+Q56</f>
+        <v>141</v>
+      </c>
+      <c r="P56" s="2">
+        <v>54</v>
+      </c>
+      <c r="Q56" s="2">
         <v>87</v>
       </c>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-    </row>
-    <row r="57" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T56" s="2">
+        <v>73.5</v>
+      </c>
+      <c r="V56" s="2">
+        <f>L56*0.3+T56*0.7</f>
+        <v>78.75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B57" s="30" t="s">
+      <c r="B57" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="46" t="s">
         <v>162</v>
       </c>
       <c r="D57" s="10"/>
       <c r="E57" s="10">
         <v>53</v>
       </c>
-      <c r="F57" s="10"/>
+      <c r="F57" s="10">
+        <v>0</v>
+      </c>
       <c r="G57" s="10">
         <v>82</v>
       </c>
       <c r="H57" s="10"/>
-      <c r="I57" s="10">
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+      <c r="L57" s="47">
+        <v>43</v>
+      </c>
+      <c r="M57" s="51"/>
+      <c r="N57" s="2">
+        <f>E57*0.3+F57*0.5+G57*0.2+J57+K57</f>
+        <v>32.299999999999997</v>
+      </c>
+      <c r="O57" s="2">
+        <f>P57+Q57</f>
         <v>0</v>
       </c>
-      <c r="J57" s="52">
+      <c r="P57" s="43">
         <v>0</v>
       </c>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
-    </row>
-    <row r="58" spans="1:13" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.15">
+      <c r="Q57" s="2">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2">
+        <v>67.5</v>
+      </c>
+      <c r="V57" s="2">
+        <f>L57*0.3+T57*0.7</f>
+        <v>60.15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.15">
       <c r="B58" s="11"/>
       <c r="C58" s="12"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A59" s="38" t="s">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="A59" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="B59" s="38"/>
-      <c r="C59" s="38"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="38"/>
-      <c r="K59" s="38"/>
-      <c r="L59" s="38"/>
-      <c r="M59" s="20"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A60" s="39" t="s">
+      <c r="B59" s="66"/>
+      <c r="C59" s="66"/>
+      <c r="D59" s="66"/>
+      <c r="E59" s="66"/>
+      <c r="F59" s="66"/>
+      <c r="G59" s="66"/>
+      <c r="H59" s="66"/>
+      <c r="I59" s="66"/>
+      <c r="J59" s="66"/>
+      <c r="K59" s="66"/>
+      <c r="L59" s="66"/>
+      <c r="M59" s="32"/>
+      <c r="N59" s="32"/>
+      <c r="O59" s="32"/>
+      <c r="P59" s="32"/>
+      <c r="Q59" s="20"/>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="A60" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="40"/>
+      <c r="B60" s="68"/>
       <c r="C60" s="6" t="s">
         <v>12</v>
       </c>
@@ -3351,37 +4498,45 @@
       <c r="G60" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H60" s="39" t="s">
+      <c r="H60" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="I60" s="41"/>
-      <c r="J60" s="40"/>
-      <c r="K60" s="42" t="s">
+      <c r="I60" s="69"/>
+      <c r="J60" s="68"/>
+      <c r="K60" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="L60" s="42"/>
-      <c r="M60" s="21"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A61" s="33"/>
-      <c r="B61" s="33"/>
+      <c r="L60" s="70"/>
+      <c r="M60" s="41"/>
+      <c r="N60" s="41"/>
+      <c r="O60" s="41"/>
+      <c r="P60" s="41"/>
+      <c r="Q60" s="21"/>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.15">
+      <c r="A61" s="62"/>
+      <c r="B61" s="62"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
       <c r="E61" s="13"/>
       <c r="F61" s="14"/>
       <c r="G61" s="14"/>
-      <c r="H61" s="34"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="36"/>
-      <c r="K61" s="33"/>
-      <c r="L61" s="33"/>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="H61" s="63"/>
+      <c r="I61" s="64"/>
+      <c r="J61" s="65"/>
+      <c r="K61" s="62"/>
+      <c r="L61" s="62"/>
+      <c r="M61" s="42"/>
+      <c r="N61" s="42"/>
+      <c r="O61" s="42"/>
+      <c r="P61" s="42"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.15">
       <c r="B62" s="24"/>
       <c r="C62" s="25"/>
       <c r="D62" s="26"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.15">
       <c r="B64" s="15" t="s">
         <v>19</v>
       </c>
@@ -3395,37 +4550,13 @@
       <c r="K64" s="22"/>
       <c r="L64" s="22"/>
       <c r="M64" s="23"/>
+      <c r="N64" s="23"/>
+      <c r="O64" s="23"/>
+      <c r="P64" s="23"/>
+      <c r="Q64" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D3:K3"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="K4:K5"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="H61:J61"/>
     <mergeCell ref="K61:L61"/>
@@ -3441,10 +4572,43 @@
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="C53:C55"/>
     <mergeCell ref="D54:D55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A51:Q51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D3:K3"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
+  <conditionalFormatting sqref="V6:V57">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>60</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.10972222222222222" right="0.10972222222222222" top="0.38124999999999998" bottom="0.5" header="0.38124999999999998" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="49" max="16383" man="1"/>
   </rowBreaks>
